--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0043.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0043.xlsx
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Ta tưởng cậu sẽ hứng thú với những gì ta đề nghị chứ! Sự chấp nhận, sự thừa nhận, sự không thể thiếu... Cậu thấy mọi người yêu quý cậu thế nào chưa? Đây chẳng phải giấc mơ thành hiện thực sao?</t>
+          <t>Tao tưởng cậu sẽ hứng thú với những gì tao đề nghị chứ! Sự chấp nhận, sự thừa nhận, sự không thể thiếu... Cậu thấy mọi người yêu quý cậu thế nào chưa? Đây chẳng phải giấc mơ thành hiện thực sao?</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Đồ khốn nạn! Ngươi nghĩ ngươi có thể phá vỡ phòng tuyến của chúng ta nhanh thế này mà không có ai phản bội Padrino à?</t>
+          <t>Đồ khốn nạn! Mày nghĩ mày có thể phá vỡ phòng tuyến của chúng tao nhanh thế này mà không có ai phản bội Padrino à?</t>
         </is>
       </c>
     </row>
@@ -4090,7 +4090,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Cậu sinh ra đâu phải để quyết định chuyện gia đình. Cậu thực sự có đủ sức để thay đổi trật tự sao?</t>
+          <t>Mày sinh ra đâu phải để quyết định chuyện gia đình. Mày thực sự có đủ sức để thay đổi trật tự sao?</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Ta méc cô bảo mẫu đấy!</t>
+          <t>Tao méc cô bảo mẫu đấy!</t>
         </is>
       </c>
     </row>
@@ -9168,7 +9168,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>&lt;color=yellow&gt;Turn back&lt;/color&gt;, trở về nơi &lt;color=yellow&gt;you started&lt;/color&gt;, như thể tìm lại chính bản thân ban đầu.</t>
+          <t>&lt;color=yellow&gt;Quay lại&lt;/color&gt;, trở về nơi &lt;color=yellow&gt;ngươi khởi đầu&lt;/color&gt;, như thể tìm lại chính bản thân ban đầu.</t>
         </is>
       </c>
     </row>
@@ -9948,7 +9948,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Chúng đang hét lên: "Chúng ta sẽ không đầu hàng đâu!"</t>
+          <t>Chúng đang hét lên: "Chúng tao sẽ không đầu hàng đâu!"</t>
         </is>
       </c>
     </row>
@@ -13198,7 +13198,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Okay.</t>
+          <t>Ừ.</t>
         </is>
       </c>
     </row>
@@ -14043,7 +14043,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Ui... híc! Dạo này ta cứ thấy khó chịu trong người, đầu óc choáng váng. Có khi không kịp ra tay khi cậu cần đấy!</t>
+          <t>Ui... híc! Dạo này tao cứ thấy khó chịu trong người, đầu óc choáng váng. Có khi không kịp ra tay khi cậu cần đấy!</t>
         </is>
       </c>
     </row>
@@ -14433,7 +14433,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Thôi, việc này ta giao cho ngươi rồi. Nhưng mà, nếu cần giúp đỡ gì thì cứ gọi ta nhé, được không?</t>
+          <t>Thôi, việc này tao giao cho mày rồi. Nhưng mà, nếu cần giúp đỡ gì thì cứ gọi tao nhé, được không?</t>
         </is>
       </c>
     </row>
@@ -14955,7 +14955,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Hay là để ta chứng minh xem ta có thể đáng tin cậy với gia đình cậu đến mức nào? Cứ thử đi, thử ta xem.</t>
+          <t>Hay là để tao chứng minh xem tao có thể đáng tin cậy với gia đình cậu đến mức nào? Cứ thử đi, thử tao xem.</t>
         </is>
       </c>
     </row>
@@ -15410,7 +15410,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Cô ấy có thể không mang họ Montelli, nhưng lại có tinh thần tiên phong y như vậy. Giờ đây, cô đang dẫn dắt một đội Cộng Hưởng Giả săn lùng Tacet Discord ngoài hoang dã.</t>
+          <t>Cô ấy có thể không mang họ Montelli, nhưng lại có tinh thần tiên phong y như vậy. Giờ đây, cô đang dẫn dắt một đội Resonator săn lùng Tacet Discord ngoài hoang dã.</t>
         </is>
       </c>
     </row>
@@ -15670,7 +15670,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Nghe đồn Montelli và Hội có mối quan hệ mật thiết hơn họ để lộ ra... Nhưng ta không dám cá đâu.</t>
+          <t>Nghe đồn Montelli và Hội có mối quan hệ mật thiết hơn họ để lộ ra... Nhưng tao không dám cá đâu.</t>
         </is>
       </c>
     </row>
@@ -16645,7 +16645,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Thôi, ta tưởng chuyện đó đã ngã ngũ rồi chứ? Sao giờ lại nhắc lại làm gì?</t>
+          <t>Thôi, tao tưởng chuyện đó đã ngã ngũ rồi chứ? Sao giờ lại nhắc lại làm gì?</t>
         </is>
       </c>
     </row>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Ta có linh cảm người đứng đầu tiếp theo sẽ là ai đó khác.</t>
+          <t>Tao có linh cảm người đứng đầu tiếp theo sẽ là ai đó khác.</t>
         </is>
       </c>
     </row>
@@ -16775,7 +16775,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Ha, thế à, nếu ngươi chắc chắn như vậy, thì nói ta xem liệu chúng ta có lấy được chiếc bánh Margherita đặc biệt đó không? Nghe nói hôm nay họ chỉ làm có ba mươi cái thôi.</t>
+          <t>Ha, thế à, nếu mày chắc chắn như vậy, thì nói tao xem liệu chúng ta có lấy được chiếc bánh Margherita đặc biệt đó không? Nghe nói hôm nay họ chỉ làm có ba mươi cái thôi.</t>
         </is>
       </c>
     </row>
@@ -18010,7 +18010,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Ta mê rượu ngon lắm. Đem thêm cho ta đi!</t>
+          <t>Tao mê rượu ngon lắm. Đem thêm cho tao đi!</t>
         </is>
       </c>
     </row>
@@ -18140,7 +18140,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Ha, dù ngươi đang thỏa mãn ham muốn hay đầu hàng nó, ta đều ở đây vì cả hai.</t>
+          <t>Ha, dù mày đang thỏa mãn ham muốn hay đầu hàng nó, tao đều ở đây vì cả hai.</t>
         </is>
       </c>
     </row>
@@ -18205,7 +18205,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Trên bàn có thực đơn dành cho người mới đến. Có lẽ cậu sẽ thấy món nào đó hợp khẩu vị, hoặc muốn tìm ai đó cùng mê &lt;color=yellow&gt;Scarlet Velvet Ribbon&lt;/color&gt; trước đã. Cậu thấy sao?</t>
+          <t>Trên bàn có thực đơn dành cho người mới đến. Có lẽ cậu sẽ thấy món nào đó hợp khẩu vị, hoặc muốn tìm ai đó cùng mê &lt;color=yellow&gt;Dải Nơ Nhung Đỏ&lt;/color&gt; trước đã. Cậu thấy sao?</t>
         </is>
       </c>
     </row>
@@ -18400,7 +18400,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Để ta giới thiệu bản thân một cách chính thức. Ta là Capollo Montelli, cậu của Carlotta, &lt;color=yellow&gt;son of the Padrino&lt;/color&gt;, và &lt;color=yellow&gt;the next head of the family&lt;/color&gt;.</t>
+          <t>Để ta giới thiệu bản thân một cách chính thức. Ta là Capollo Montelli, cậu của Carlotta, &lt;color=yellow&gt;con trai của Padrino&lt;/color&gt;, và &lt;color=yellow&gt;người đứng đầu gia tộc kế tiếp&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -19570,7 +19570,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Giờ cậu nhắc đến mới nói, để ta nói rõ cho.</t>
+          <t>Giờ cậu nhắc đến mới nói, để tao nói rõ cho.</t>
         </is>
       </c>
     </row>
@@ -20155,7 +20155,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Nếu không... tin ta đi, dù cậu có mạnh đến đâu cũng đừng dại mà chống lại chúng ta.</t>
+          <t>Nếu không... tin tao đi, dù cậu có mạnh đến đâu cũng đừng dại mà chống lại chúng tao.</t>
         </is>
       </c>
     </row>
@@ -20480,7 +20480,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Tiếc nhỉ. Ta không ngờ cậu lại kéo {Male=hắn;Female=cô ta} ra nói chuyện riêng, nhất là sau tất cả những gì Rover và ta đã trải qua cùng nhau.</t>
+          <t>Tiếc nhỉ. Tao không ngờ cậu lại kéo {Male=him;Female=her} ra nói chuyện riêng, nhất là sau tất cả những gì Rover và tao đã trải qua cùng nhau.</t>
         </is>
       </c>
     </row>
@@ -20675,7 +20675,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Gặp tớ ở &lt;color=yellow&gt;rendezvous&lt;/color&gt;. Cẩn thận với những "con mắt" đó.</t>
+          <t>Gặp tớ ở &lt;color=yellow&gt;điểm hẹn&lt;/color&gt;. Cẩn thận với những "con mắt" đó.</t>
         </is>
       </c>
     </row>
@@ -22436,7 +22436,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Đây là lần thứ sáu cậu hỏi trong ba phút. Thở đi và bình tĩnh lại. Chẳng ai phát hiện ra đâu.</t>
+          <t>Đây là lần thứ sáu mày hỏi trong ba phút. Thở đi và bình tĩnh lại. Chẳng ai phát hiện ra đâu.</t>
         </is>
       </c>
     </row>
@@ -23346,7 +23346,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Xong việc này, ta sẽ đổi luôn biệt danh mới.</t>
+          <t>Xong việc này, tao sẽ đổi luôn biệt danh mới.</t>
         </is>
       </c>
     </row>
@@ -23671,7 +23671,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Dù sao thì ta chưa nghỉ hưu đâu, nhưng ta đã kiệt sức rồi. Một biệt danh mới và môi trường mới có thể giúp ta có cái nhìn mới mẻ và giữ lửa đam mê với nghề.</t>
+          <t>Dù sao thì tao chưa nghỉ hưu đâu, nhưng tao đã kiệt sức rồi. Một biệt danh mới và môi trường mới có thể giúp tao có cái nhìn mới mẻ và giữ lửa đam mê với nghề.</t>
         </is>
       </c>
     </row>
@@ -23866,7 +23866,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Được rồi, được rồi. À, ta nghe nói Septimont đang thiếu người đấy. Hay là tụi mình...</t>
+          <t>Được rồi, được rồi. À, tao nghe nói Septimont đang thiếu người đấy. Hay là tụi mình...</t>
         </is>
       </c>
     </row>
@@ -24126,7 +24126,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Có thể không phải, nhưng bà ấy đã nói rõ: dù ta làm gì đi nữa, cuối tuần nào cũng phải về nhà ăn cơm. Nếu không, bà ấy sẽ "bẻ gãy chân ta bằng cái vá và nhét đầu ta vào một tô mì Ý". Lời bà ấy, không phải của ta đâu.</t>
+          <t>Có thể không phải, nhưng bà ấy đã nói rõ: dù tao làm gì đi nữa, cuối tuần nào cũng phải về nhà ăn cơm. Nếu không, bà ấy sẽ "bẻ gãy chân tao bằng cái vá và nhét đầu tao vào một tô mì Ý". Lời bà ấy, không phải của tao đâu.</t>
         </is>
       </c>
     </row>
@@ -25101,7 +25101,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>À, vậy à. Tin đồn, chín muồi và chờ đợi, nguồn cảm hứng dạt dào trong tầm tay. Để xem nào... *"Liệu mình có thể thực sự tin tưởng {Male=hắn;Female=cô ta} không? Nàng tự hỏi. Nhưng bản năng thôi thúc nàng tiến lên. Nàng nắm chặt {Male=tay hắn;Female=tay cô ta}, rồi quay lưng, dâng trọn cho người bạn đồng hành mới."* Ừ, đúng là có triển vọng!</t>
+          <t>À, vậy à. Tin đồn, chín muồi và chờ đợi, nguồn cảm hứng dạt dào trong tầm tay. Để xem nào... *"Liệu mình có thể thực sự tin tưởng {Male=his;Female=her} không? Nàng tự hỏi. Nhưng bản năng thôi thúc nàng tiến lên. Nàng nắm chặt {Male=his;Female=her}, rồi quay lưng, dâng trọn cho người bạn đồng hành mới."* Ừ, đúng là có triển vọng!</t>
         </is>
       </c>
     </row>
@@ -27701,7 +27701,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Benett... giờ ta còn có thể moi được bí mật nào của ngươi nữa đây?</t>
+          <t>Benett... giờ tao còn có thể moi được bí mật nào của mày nữa đây?</t>
         </is>
       </c>
     </row>
@@ -28416,7 +28416,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Ta với Benett—chúng ta là đồng đội. Từ nhiệm vụ, trò nghịch ngợm, đến cả con chó chung nữa. Gia đình của nhau cũng biết hết. Đó là kiểu câu chuyện mà ngươi chỉ nghe khi hai đứa đã cùng nhau đối mặt với sinh tử.</t>
+          <t>Tao với Benett—chúng tao là đồng đội. Từ nhiệm vụ, trò nghịch ngợm, đến cả con chó chung nữa. Gia đình của nhau cũng biết hết. Đó là kiểu câu chuyện mà mày chỉ nghe khi hai đứa đã cùng nhau đối mặt với sinh tử.</t>
         </is>
       </c>
     </row>
@@ -29651,7 +29651,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Ta không thấy ai buôn bán Thiết bị đầu cuối ở đây cả.</t>
+          <t>Tao không thấy ai buôn bán Thiết bị đầu cuối ở đây cả.</t>
         </is>
       </c>
     </row>
@@ -29716,7 +29716,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Tất cả những gì ta thấy là ngươi đang cướp đoạt thứ thuộc về họ.</t>
+          <t>Tất cả những gì tao thấy là mày đang cướp đoạt thứ thuộc về họ.</t>
         </is>
       </c>
     </row>
@@ -29846,7 +29846,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Nhưng chính những &lt;color=yellow&gt;traders&lt;/color&gt; đã lấy tiền của ngươi lại nhận ra sai lầm và tố cáo giao dịch của ngươi. Họ đã thề sẽ hối cải vì sản xuất bất hợp pháp và chấm dứt mọi giao dịch với ngươi.</t>
+          <t>Nhưng chính những &lt;color=yellow&gt;thương nhân&lt;/color&gt; đã lấy tiền của ngươi lại nhận ra sai lầm và tố cáo giao dịch của ngươi. Họ đã thề sẽ hối cải vì sản xuất bất hợp pháp và chấm dứt mọi giao dịch với ngươi.</t>
         </is>
       </c>
     </row>
@@ -30301,7 +30301,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Nhớ lời ta nói! Ngày Montelli quỳ gối trước Hội và Fisalia sẽ là ngày các người phải cầu xin lòng thương xót của Sentinel.</t>
+          <t>Nhớ lời tao nói! Ngày Montelli quỳ gối trước Hội và Fisalia sẽ là ngày các người phải cầu xin lòng thương xót của Sentinel.</t>
         </is>
       </c>
     </row>
@@ -30626,7 +30626,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Nhưng vì Ernesto bảo chuyện này liên quan đến Benett, ta sẽ cho ngươi một phút, vì hắn. Nói nhanh lên.</t>
+          <t>Nhưng vì Ernesto bảo chuyện này liên quan đến Benett, tao sẽ cho mày một phút, vì hắn. Nói nhanh lên.</t>
         </is>
       </c>
     </row>
@@ -30951,7 +30951,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Chưa kể gần hai tuần nay ta còn chẳng thấy bóng dáng một tên Montelli nào.</t>
+          <t>Chưa kể gần hai tuần nay tao còn chẳng thấy bóng dáng một tên Montelli nào.</t>
         </is>
       </c>
     </row>
@@ -32186,7 +32186,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Có &lt;color=yellow&gt;an entrance along the coast&lt;/color&gt; kia. Đi thẳng theo con đường đó là thấy. Cậu đến đó có việc gì thế?</t>
+          <t>Có &lt;color=yellow&gt;một lối vào dọc bờ biển&lt;/color&gt; kia. Đi thẳng theo con đường đó là thấy. Cậu đến đó có việc gì thế?</t>
         </is>
       </c>
     </row>
@@ -32381,7 +32381,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Với anh ấy, công việc luôn là trên hết, tình bạn đứng thứ hai. Khi trễ giờ, anh ấy thường ở lại trên &lt;color=yellow&gt;hill&lt;/color&gt; kia. Sau vài lần như vậy, chúng tôi còn dựng cả một cái chòi ở đó. Chỉ thế thôi.</t>
+          <t>Với anh ấy, công việc luôn là trên hết, tình bạn đứng thứ hai. Khi trễ giờ, anh ấy thường ở lại trên &lt;color=yellow&gt;ngọn đồi&lt;/color&gt; kia. Sau vài lần như vậy, chúng tôi còn dựng cả một cái chòi ở đó. Chỉ thế thôi.</t>
         </is>
       </c>
     </row>
